--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0102.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0102.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Enhance Tips</t>
+          <t>Mẹo Nâng cấp</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Enhance Tips</t>
+          <t>Mẹo Nâng cấp</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Equipment Tips</t>
+          <t>Mẹo Trang Bị</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Xác nhận Bản ghi</t>
+          <t>Xác nhận sao lưu</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Xác nhận Bản ghi</t>
+          <t>Xác nhận sao lưu</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Syntonize</t>
+          <t>Điều tần</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Weapon Replacement</t>
+          <t>Thay Thế Vũ Khí</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Syntonize</t>
+          <t>Điều tần</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Syntonize</t>
+          <t>Điều tần</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Syntonize</t>
+          <t>Điều tần</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Xác nhận Tiêm</t>
+          <t>Xác nhận tiêm</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Kết thúc và hoàn tất</t>
+          <t>Kết thúc và Xác nhận</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Quay lại Màn hình Đăng nhập</t>
+          <t>Quay Lại Màn Hình Đăng Nhập</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Hệ thống Thông báo</t>
+          <t>Thông Báo Hệ Thống</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Làm mới Shop</t>
+          <t>Làm mới cửa hàng</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Accessory Replacement Thông báo</t>
+          <t>Thông báo Thay thế Trang sức</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Tiến hành Tải xuống</t>
+          <t>Tiến hành tải xuống</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Mở Kho</t>
+          <t>Mở Kho Đồ</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Warehouse Full</t>
+          <t>Kho Đồ Đã Đầy</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Dùng mạng di động để tải xuống</t>
+          <t>Tải xuống qua mạng di động</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Trang bị Namipon</t>
+          <t>Gắn Namipon</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Tải xuống bằng mạng di động</t>
+          <t>Tải xuống qua mạng di động</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Xác nhận Từ bỏ</t>
+          <t>Xác nhận Bỏ Cuộc</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Từ bỏ Nhiệm vụ</t>
+          <t>Hủy Nhiệm Vụ</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Xóa email hiện tại</t>
+          <t>Xóa thư này</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Server Shutdown Thông báo</t>
+          <t>Thông Báo Đóng Máy Chủ</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Tên có thể dài tối đa 6 ký tự Trung Quốc hoặc 12 chữ cái</t>
+          <t>Tên có thể dài tối đa 6 ký tự Trung Quốc hoặc 12 chữ cái.</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Lưu</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Lưu kế hoạch đã thay đổi</t>
+          <t>Giữ nguyên kế hoạch đã thay đổi</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Mời người chơi khác trong nhóm</t>
+          <t>Mời các thành viên khác trong nhóm</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Dữ liệu Triệu Tập đã được làm mới</t>
+          <t>Dữ liệu Hội Tụ đã được làm mới</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Số lần Triệu Tập cho Banner này đã đạt giới hạn hôm nay</t>
+          <t>Số lần Triệu Hoán cho Banner này hôm nay đã đạt giới hạn</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Khôi phục dữ liệu hoàn tất</t>
+          <t>Dữ liệu đã được khôi phục</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Đặt lại nút</t>
+          <t>Điểm nút đã được đặt lại</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Loại thành viên này khỏi Co-op</t>
+          <t>Loại thành viên này khỏi nhóm Đồng Hành</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Thử lại</t>
+          <t>Thử Lại</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Bỏ cuộc thử thách</t>
+          <t>Bỏ cuộc đi!</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Temporarily Exit</t>
+          <t>Thoát Tạm Thời</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Rời Tháp Nghịch Cảnh</t>
+          <t>Rời khỏi Tháp Nghịch Cảnh đi</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Xác nhận mô phỏng lại</t>
+          <t>Xác nhận tái mô phỏng</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Đặt lại Confirmation</t>
+          <t>Xác nhận đặt lại</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Tháp Nghịch Cảnh chưa mở</t>
+          <t>Tháp Nghịch Cảnh vẫn chưa mở</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Triển khai Confirmation</t>
+          <t>Xác nhận triển khai</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Abandon Exploration</t>
+          <t>Rời khỏi Thám Hiểm</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Tiếp tục Exploration</t>
+          <t>Tiếp tục khám phá</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Temporarily Exit</t>
+          <t>Thoát Tạm Thời</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Exit Confirmation</t>
+          <t>Xác Nhận Thoát</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Tiếp tục Exploration</t>
+          <t>Tiếp tục khám phá</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Trở về mặt đất</t>
+          <t>Quay trở lại mặt đất</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Exit Confirmation</t>
+          <t>Xác Nhận Thoát</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Xóa Ghi chú này</t>
+          <t>Xóa Ghi Chú này</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Quay lại Đăng nhập</t>
+          <t>Quay Lại Màn Hình Đăng Nhập</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Thử Thách Cá Nhân</t>
+          <t>Thử Thách Solo</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Invite Teammate</t>
+          <t>Mời đồng đội</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Tìm trận đấu</t>
+          <t>Tìm Match</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Invite</t>
+          <t>Mời</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Thành công</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Đối tượng địa hình không tồn tại</t>
+          <t>Vật thể địa hình không tồn tại</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Loại đối tượng địa hình không đúng</t>
+          <t>Loại đối tượng địa hình không hợp lệ</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Loại thao tác đối tượng địa hình không đúng</t>
+          <t>Loại thao tác đối tượng địa hình không hợp lệ</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Lỗi trạng thái đối tượng địa hình</t>
+          <t>Lỗi trạng thái vật thể địa hình</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Không tìm thấy thực thể thay đổi trạng thái</t>
+          <t>Không tìm thấy thực thể cần thay đổi trạng thái</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Trạng thái thực thể thay đổi không tồn tại</t>
+          <t>Thực thể thay đổi trạng thái không tồn tại</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Không khớp trạng thái thay đổi</t>
+          <t>Lệnh thay đổi trạng thái không khớp</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>So khớp thay đổi trạng thái cũ và mới</t>
+          <t>Đang đối chiếu thay đổi trạng thái cũ và mới</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Đã đăng ký đầy</t>
+          <t>Đăng ký đã đầy</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Không thể thay đổi trạng thái khi bị Silence</t>
+          <t>Không thể thay đổi trạng thái khi đang im lặng</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Không thể thay đổi khi ở trạng thái spawn</t>
+          <t>Không thể thay đổi khi đang ở trạng thái hồi sinh</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Điều kiện thay đổi trạng thái chưa đáp ứng</t>
+          <t>Chưa đủ điều kiện để thay đổi trạng thái</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Thiếu người chơi console để thay đổi trạng thái</t>
+          <t>Thiếu người chơi điều khiển cho thay đổi trạng thái</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Thực thể cơ sở Levitation không tồn tại</t>
+          <t>Đế nâng bay không tồn tại</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Hãy tạo hồ sơ người chơi trước</t>
+          <t>Hãy tạo hồ sơ người chơi trước đã</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Thiếu thành phần Foundation cho thực thể cơ sở Levitation</t>
+          <t>Thiếu thành phần Foundation của thực thể Levitation</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Đã kích hoạt thực thể cơ sở Levitation</t>
+          <t>Đế nâng bay đã kích hoạt</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Thực thể cơ sở Levitation không hoạt động</t>
+          <t>Đế nâng bay chưa được kích hoạt</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Puzzle trọng lực không tồn tại</t>
+          <t>Không có cái gọi là câu đố trọng lực</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Thiếu thành phần puzzle trọng lực</t>
+          <t>Thiếu thành phần câu đố trọng lực</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Thiếu ID cơ sở Mutterfly</t>
+          <t>Thiếu ID Mutterfly cơ bản</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Thiếu cơ sở Mutterfly</t>
+          <t>Thiếu Mutterfly cơ bản</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Cơ sở Mutterfly đã kích hoạt</t>
+          <t>Trạm Mutterfly đã kích hoạt</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Thực thể động vật nhỏ bị phá hủy không tồn tại</t>
+          <t>Động vật nhỏ mà phá hủy cả thực thể không tưởng</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Cây hành vi ẩn nấp không tồn tại</t>
+          <t>Cây hành vi tàng hình không tồn tại</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Các nút cây hành vi ẩn nấp không tồn tại</t>
+          <t>Các nút hành vi tàng hình không tồn tại</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Không thể tạo hồ sơ người chơi</t>
+          <t>Không tạo được hồ sơ người chơi</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Nút ẩn nấp không phải là nút thất bại</t>
+          <t>Nút tàng hình không phải là nút thất bại</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Thiếu cấu hình thời gian ẩn nấp</t>
+          <t>Thiếu cấu hình thời gian tàng hình</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Lỗi cấu hình ẩn nấp</t>
+          <t>Lỗi cấu hình tàng hình</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Đã ở chế độ ẩn nấp</t>
+          <t>Đang ở chế độ tàng hình rồi</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Không ở chế độ ẩn nấp</t>
+          <t>Không ở chế độ tàng hình</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Thực thể điều khiển đã có bộ điều khiển</t>
+          <t>Thực thể điều khiển đã có người điều khiển</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Không thể tạo hồ sơ người chơi</t>
+          <t>Không tạo được hồ sơ người chơi</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Cây hành vi hiện tại không ở chế độ ẩn nấp</t>
+          <t>Cây hành vi hiện tại không ở chế độ tàng hình</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Điều kiện di chuyển không đáp ứng</t>
+          <t>Điều kiện di chuyển chưa đạt</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Thiếu cấu hình Bay Lượn</t>
+          <t>Thiếu cấu hình Levitation</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Re-login</t>
+          <t>Đăng Nhập Lại</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Yêu cầu dữ liệu người dùng thất bại</t>
+          <t>Không thể yêu cầu dữ liệu người dùng</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Xác minh dữ liệu người dùng thất bại</t>
+          <t>Không thể xác minh dữ liệu người dùng</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Tham số GM không đúng</t>
+          <t>Tham số GM sai</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Không có nhóm điều hướng đang chạy</t>
+          <t>Nhóm dẫn đường không được chạy nhé.</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Không thể hoàn thành quy trình hướng dẫn giám sát máy chủ</t>
+          <t>Không thể hoàn tất quy trình hướng dẫn giám sát máy chủ</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Hướng dẫn kích hoạt hiện tại không có trong danh sách chờ</t>
+          <t>Hướng dẫn kích hoạt hiện tại không nằm trong danh sách chờ</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Kích hoạt lặp lại cho bước hướng dẫn</t>
+          <t>Kích hoạt lại để tiếp tục bước hướng dẫn</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Không thể kích hoạt lặp lại nhóm hướng dẫn</t>
+          <t>Không thể kích hoạt lại nhóm hướng dẫn</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Cấu hình hướng dẫn không tồn tại</t>
+          <t>Cấu Hình Hướng Dẫn Không Tồn Tại</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Hướng dẫn đã khóa</t>
+          <t>Hướng Dẫn Đã Bị Khóa</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng hướng dẫn</t>
+          <t>Đã nhận phần thưởng hướng dẫn rồi</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Cấu hình rơi thưởng hướng dẫn không tồn tại</t>
+          <t>Cấu Hình Phần Thưởng Hướng Dẫn Không Tồn Tại</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Lỗi phân phối rơi thưởng hướng dẫn</t>
+          <t>Lỗi Phân Phát Phần Thưởng Hướng Dẫn</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>ID nhóm hướng dẫn hiện tại không khớp</t>
+          <t>ID nhóm hướng dẫn hiện tại không khớp.</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Loại mục chỉ mục yêu cầu không tồn tại</t>
+          <t>Loại chỉ mục yêu cầu không tồn tại</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Mục chỉ mục đã khóa</t>
+          <t>Mục lục bị khóa</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Không thể mở khóa loại mục hiện tại</t>
+          <t>Loại mục này hiện không thể mở khóa</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Số lượng yêu cầu vượt quá số lượng chỉ mục tối đa</t>
+          <t>Số lượng yêu cầu vượt quá giới hạn chỉ mục tối đa</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Số lượng Resonator trong đội hình không chính xác</t>
+          <t>Số lượng Resonator trong đội hình không đúng</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Sự kiện không khả dụng</t>
+          <t>Sự kiện chưa khả dụng</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng</t>
+          <t>Đã nhận rồi</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Thử thách bị khóa</t>
+          <t>Thách đấu bị khóa</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng</t>
+          <t>Đã nhận rồi</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng</t>
+          <t>Đã nhận rồi</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng</t>
+          <t>Đã nhận rồi</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Lỗi thực thi GM</t>
+          <t>LỖI THỰC THI QUẢN TRỊ VIÊN</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Phải là bạn bè với người chơi để bắt đầu trò chuyện riêng</t>
+          <t>Phải là bạn bè với người chơi mới bắt đầu trò chuyện riêng tư</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Biểu cảm không khả dụng</t>
+          <t>Không thể biểu cảm</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Quá nhiều yêu cầu</t>
+          <t>Quá nhiều yêu cầu.</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Chưa mở khóa Câu chuyện Nhân vật</t>
+          <t>Câu chuyện Nhân vật chưa mở khóa</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Đã đạt số lượng Câu chuyện Nhân vật đồng thời tối đa</t>
+          <t>Đã đạt số lượng Câu Chuyện Nhân Vật tối đa có thể kích hoạt đồng thời</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng</t>
+          <t>Đã nhận phần thưởng</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Thêm GameplayEffect thất bại</t>
+          <t>Không thể thêm Hiệu Ứng Chơi.</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Thực thể thoát chiến không phải quái vật</t>
+          <t>Không thể thoát chiến đấu: Đối tượng không phải quái vật</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Thực thể tự hủy không tồn tại</t>
+          <t>Không tồn tại thực thể tự hủy</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Thực thể tự hủy đã bị loại bỏ</t>
+          <t>Thực thể tự hủy đã sụp đổ</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Không tìm thấy đơn hàng</t>
+          <t>Không tìm thấy Lệnh</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Đơn hàng không khớp với người chơi</t>
+          <t>Lệnh không khớp với người chơi</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Không thể cập nhật đơn hàng sang trạng thái đã xử lý</t>
+          <t>Không thể cập nhật trạng thái Lệnh thành đã xử lý</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Cập nhật đơn hàng sang trạng thái đã xử lý thất bại</t>
+          <t>Không thể cập nhật trạng thái Lệnh thành đã xử lý</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Cấu hình Triệu Tập không tồn tại</t>
+          <t>Cấu hình Triệu hồi không tồn tại.</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Cấu hình nhóm quy tắc Triệu Tập không tồn tại</t>
+          <t>Cấu hình nhóm quy tắc Triệu hồi không tồn tại.</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Cấu hình quy tắc Triệu Tập không tồn tại</t>
+          <t>Cấu hình quy tắc Triệu hồi không tồn tại.</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Loại Triệu Tập không xác định</t>
+          <t>Loại Triệu Hồi Không xác định</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Số lần thử còn lại trong ngày của bể Triệu Tập hiện tại không đủ</t>
+          <t>Đã hết lượt triệu hồi trong bể Convene hôm nay.</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Tổng số lần thử còn lại của bể Triệu Tập hiện tại không đủ</t>
+          <t>Số lần còn lại cho đợt Triệu Tập hiện tại không đủ.</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Tổng số lần thử Triệu Tập còn lại không đủ</t>
+          <t>Số lần Triệu Tập còn lại không đủ.</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Bể Triệu Tập hiện tại không khả dụng</t>
+          <t>Bể Triệu Hồi hiện không khả dụng</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Bể Triệu Tập hiện tại đã đóng</t>
+          <t>Bể Triệu Hồi hiện đã đóng</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Chức năng Triệu Tập đã bị vô hiệu hóa</t>
+          <t>Chức năng Triệu hồi đã bị vô hiệu hóa.</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Cấu hình trao đổi vật phẩm không tồn tại</t>
+          <t>Không tìm thấy cấu hình trao đổi vật phẩm</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Số lần đổi quà hôm nay không đủ</t>
+          <t>Hôm nay đã hết lượt đổi quà.</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Tổng số lần đổi quà không đủ</t>
+          <t>Số lần chuộc tổng không đủ.</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Thông tin giới hạn Triệu Tập không tồn tại</t>
+          <t>Thông tin giới hạn Triệu hồi không tồn tại.</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Danh sách thông tin giới hạn Triệu Hoán còn thiếu</t>
+          <t>Danh sách giới hạn Triệu Tập bị thiếu</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Dữ liệu Triệu Hoán bất thường, vui lòng thử lại sau</t>
+          <t>Dữ liệu Gacha bất thường, vui lòng thử lại sau</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Chức năng Triệu Hoán chưa được kích hoạt</t>
+          <t>Chức năng Triệu hồi chưa được kích hoạt.</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Triệu Hoán hiện tại chưa được kích hoạt</t>
+          <t>Gacha hiện tại chưa được kích hoạt</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Dữ liệu Triệu Hoán bất thường, vui lòng thử lại sau</t>
+          <t>Dữ liệu Gacha bất thường, vui lòng thử lại sau</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Dữ liệu Triệu Hoán bất thường, vui lòng thử lại sau</t>
+          <t>Dữ liệu Gacha bất thường, vui lòng thử lại sau</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Vui lòng chọn thông tin Triệu Hoán cho lần Triệu Hoán mục tiêu trước</t>
+          <t>Hãy chọn thông tin triệu hồi cho Convene mục tiêu trước</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng</t>
+          <t>Đã nhận phần thưởng</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Lỗi thứ tự nhận thưởng</t>
+          <t>Lỗi yêu cầu nhận thưởng.</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Chưa chọn ID phát hiện hiện tại</t>
+          <t>Chưa chọn ID phát hiện hiện tại.</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Danh sách ID mẫu phát hiện quái vật không bình thường không được để trống</t>
+          <t>Danh sách ID mẫu phát hiện quái vật bất thường không được để trống</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Lỗi bật/tắt trạng thái</t>
+          <t>Lỗi chuyển đổi trạng thái</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Lỗi bật/tắt trạng thái</t>
+          <t>Lỗi chuyển đổi trạng thái</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Lỗi bật/tắt trạng thái</t>
+          <t>Lỗi chuyển đổi trạng thái</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Tính năng hoạt động bị vô hiệu hóa</t>
+          <t>Chức năng Hoạt Động đã bị vô hiệu hóa</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình nhiệm vụ hoạt động</t>
+          <t>Không tìm thấy cấu hình nhiệm vụ Hoạt Động</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Chưa nhận nhiệm vụ hoạt động</t>
+          <t>Chưa nhận nhiệm vụ Hoạt Động</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Nhiệm vụ hoạt động chưa hoàn thành</t>
+          <t>Nhiệm vụ Hoạt Động chưa hoàn thành</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng điều kiện yêu cầu</t>
+          <t>Chưa đủ điều kiện</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Lỗi tham số yêu cầu phần thưởng nhiệm vụ hoạt động</t>
+          <t>Lỗi tham số yêu cầu phần thưởng nhiệm vụ Hoạt Động</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Thiếu cấu hình phần thưởng</t>
+          <t>Thiếu cấu hình phần thưởng.</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Thiếu cấu hình phần thưởng</t>
+          <t>Thiếu cấu hình phần thưởng.</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Bạn chưa điểm danh</t>
+          <t>Bạn chưa đăng nhập.</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Thiếu cấu hình phần thưởng</t>
+          <t>Thiếu cấu hình phần thưởng.</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Chưa đủ điểm yêu cầu</t>
+          <t>Chưa Đủ Điểm Yêu Cầu</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Chưa đến thời gian sự kiện</t>
+          <t>Chưa đến giờ sự kiện mà.</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Sự kiện chưa khả dụng</t>
+          <t>Sự kiện không khả dụng</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Insufficient Decipher items</t>
+          <t>Vật phẩm Giải Mã không đủ</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Tất cả Lunar Phases deciphered</t>
+          <t>Đã giải mã toàn bộ Pha Mặt Trăng</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Event data error</t>
+          <t>Lỗi dữ liệu sự kiện</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Event data error</t>
+          <t>Lỗi dữ liệu sự kiện</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Event data error</t>
+          <t>Lỗi dữ liệu sự kiện</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng</t>
+          <t>Đã nhận phần thưởng rồi</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng</t>
+          <t>Đã nhận phần thưởng rồi</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Không thể nhận vật phẩm Giải Mã</t>
+          <t>Không nhận được vật phẩm Giải Mã</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Không thể nhận Lunar Blessings</t>
+          <t>Không nhận được Phước Lành Mặt Trăng</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Giới hạn cấp độ Vũ khí</t>
+          <t>Giới Hạn Cấp Độ Vũ Khí</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Giới hạn Rank Vũ khí</t>
+          <t>Giới Hạn Cấp Vũ Khí</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Insufficient Consumables</t>
+          <t>Vật phẩm Tiêu Hao không đủ</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Kho Vũ khí đã đầy</t>
+          <t>Kho Vũ Khí Đã Đầy</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Cấp độ quá thấp để tăng Rank</t>
+          <t>Cấp độ quá thấp, không thể tăng Hạng.</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Cấp độ quá thấp để tăng Rank</t>
+          <t>Cấp độ quá thấp, không thể tăng Hạng.</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Lỗi thực thi chức năng</t>
+          <t>Lỗi hàm Thi Hành</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Nhân vật không khả dụng để trao đổi</t>
+          <t>{CharacterName} không thể trao đổi.</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng điều kiện mở khóa</t>
+          <t>Chưa đủ điều kiện mở khóa</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Invalid EXP</t>
+          <t>Điểm kinh nghiệm không hợp lệ</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,9 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Không đủ nguyên liệu kích hoạt
----
-**Giữ nguyên (không dịch):**</t>
+          <t>Vật liệu kích hoạt không đủ.</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31236,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Lỗi tham số giao thức</t>
+          <t>Lỗi Tham Số Giao Thức</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31306,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Empty Consumable Inventory</t>
+          <t>Kho vật phẩm tiêu hao trống</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31376,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Đã đạt số lượng tối đa Vật phẩm Tiêu hao trong Kho Vật phẩm Tiêu hao</t>
+          <t>Quá nhiều Vật Phẩm Tiêu Hao trong Kho Vật Phẩm Tiêu Hao</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31446,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Lỗi tính toán Vật phẩm Kinh nghiệm</t>
+          <t>Lỗi tính toán vật phẩm tiêu hao Kinh Nghiệm</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31516,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Vị trí Echo không hợp lệ</t>
+          <t>Vị trí Echo sai</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31656,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Không có Echo để gỡ bỏ</t>
+          <t>Không có Echo để gỡ bỏ.</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31726,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Không đủ Vật phẩm Kinh nghiệm</t>
+          <t>Vật phẩm Kinh nghiệm không đủ.</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31796,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Thân mật không đủ để đổi tên Resonator này</t>
+          <t>Mức Thân Mật chưa đủ để đổi tên Resonator này.</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31936,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Nút chưa được kích hoạt</t>
+          <t>Điểm nút chưa kích hoạt</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32146,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Dữ liệu khu vực của nhân vật thử nghiệm đã tồn tại</t>
+          <t>Dữ liệu khu vực nhân vật thử nghiệm đã tồn tại</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32216,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Dữ liệu cây hành vi của nhân vật thử nghiệm đã tồn tại</t>
+          <t>Dữ liệu cây hành vi nhân vật thử nghiệm đã tồn tại</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32286,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Khu vực của nhân vật thử nghiệm đã tồn tại</t>
+          <t>Khu vực nhân vật thử nghiệm đã tồn tại</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32356,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Khu vực của nhân vật thử nghiệm không tồn tại</t>
+          <t>Khu vực nhân vật thử nghiệm không tồn tại</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32566,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Nhân vật không hợp lệ để trang bị</t>
+          <t>Nhân vật không phù hợp để trang bị</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32636,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Lỗi cấu hình nhân vật cho trang bị</t>
+          <t>Lỗi cấu hình trang bị cho nhân vật</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32706,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Cấu hình Echo rỗng</t>
+          <t>Cấu hình Null Echo</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32916,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Vật phẩm tăng cấp Echo không khớp với cấu hình</t>
+          <t>Vật phẩm nâng cấp Echo không khớp với cấu hình</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32986,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Kinh nghiệm không tăng do không chọn vật phẩm hoặc vật phẩm không khớp với cấu hình</t>
+          <t>Kinh Nghiệm tăng 0 do không chọn vật phẩm hoặc vật phẩm chọn không khớp cấu hình</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33056,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Cấp độ dự kiến vượt quá cấp độ tối đa</t>
+          <t>Cấp độ dự kiến vượt quá cấp tối đa</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33196,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Vị trí Echo không đúng</t>
+          <t>Vị trí Echo sai</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33546,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Cấu hình tăng cấp Rank Echo không tồn tại</t>
+          <t>Cấu hình nâng cấp Cấp Tần Số không tồn tại</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33616,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Cấp độ Echo không đủ</t>
+          <t>Cấp Độ Echo không đủ.</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33686,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Vật phẩm EXP Echo không tồn tại</t>
+          <t>Vật phẩm Điểm Kinh Nghiệm Cộng Hưởng không tồn tại</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33826,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Không đủ mục chỉ số phụ Echo</t>
+          <t>Số lượng thuộc tính phụ Echo không đủ.</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33966,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Cấu hình tăng cấp Echo không tồn tại</t>
+          <t>Cấu Hình Tăng Cấp Tiếng Vọng Không Tồn Tại</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34036,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Không đủ vật phẩm tiêu hao để tăng cấp Echo</t>
+          <t>Không đủ vật phẩm tiêu hao để nâng cấp Echo</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34106,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Vật liệu Echo bị khóa</t>
+          <t>Nguyên liệu Echo bị khóa</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34176,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Vật liệu tăng cấp Echo không khớp</t>
+          <t>Vật Liệu Tăng Cấp Tiếng Vọng Không Khớp</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34246,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Vật liệu Echo đã được chọn</t>
+          <t>Nguyên liệu Echo đã được chọn</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34386,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Số lượng vật liệu tăng cấp Rank Echo không chính xác</t>
+          <t>Lỗi số lượng nguyên liệu nâng cấp Cấp Tần Số</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34456,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Vật liệu tăng cấp Rank Echo đã được chọn</t>
+          <t>Nguyên liệu nâng cấp Cấp Tần Số đã được chọn</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34526,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Echo đang trang bị không thể Phân giải</t>
+          <t>Echo đã trang bị không thể Phế Diệt</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34596,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Có Echo không thể tái chế</t>
+          <t>Bao Gồm Tiếng Vọng Không Thể Tái Chế</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34666,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Có vật phẩm đang trang bị</t>
+          <t>Bao gồm vật phẩm đã trang bị</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34736,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Lỗi vật liệu tăng cấp Rank Echo</t>
+          <t>Lỗi nguyên liệu nâng cấp Cấp Tần Số</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34806,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Chưa có dữ liệu gợi ý Echo cho Resonator này</t>
+          <t>Chưa có dữ liệu gợi ý Echo cho Resonator này.</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -35226,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Không thể phân giải vật phẩm này</t>
+          <t>Không thể phân giải vật phẩm</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35296,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Cấp độ quá thấp để sử dụng vật phẩm</t>
+          <t>Cấp độ quá thấp, không thể sử dụng vật phẩm.</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35366,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Không thể khóa vật phẩm này</t>
+          <t>Không thể khóa vật phẩm</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35436,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Số lượng phần thưởng bạn chọn không đúng</t>
+          <t>Số lượng phần thưởng bạn chọn không hợp lệ.</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35506,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Phần thưởng bạn chọn không tồn tại</t>
+          <t>Phần thưởng bạn chọn không tồn tại.</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
